--- a/mock/sample_holdings_error.xlsx
+++ b/mock/sample_holdings_error.xlsx
@@ -99,6 +99,16 @@
           <t xml:space="preserve">자산군</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계좌종류</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">비고</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -695,92 +705,138 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계좌종류</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">증권 마스터에 등록된 계좌종류 (예: 일반(위탁), ISA, 연금저축). 비우면 같은 이름 계좌의 기존 값 유지</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">허용값</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">통화</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KRW, USD</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">비고</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">선택</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계좌 메모. 계좌의 아무 행에 한 번만 적어도 됩니다. 비우면 기존 비고 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">거래소</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NASDAQ, NYSE, KRX, UPBIT, CASH</t>
+          <t xml:space="preserve">허용값</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">자산유형</t>
+          <t xml:space="preserve">통화</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETF, STOCK, CRYPTO, GOLD, CASH</t>
+          <t xml:space="preserve">KRW, USD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">자산군</t>
+          <t xml:space="preserve">거래소</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASH(현금성), LEVERAGE(레버리지), NASDAQ100(나스닥1배), SP500(S&amp;P500), OTHER_STOCK(기타종목), GOLD(금), BLOCKCHAIN(블록체인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
+          <t xml:space="preserve">NASDAQ, NYSE, KRX, UPBIT, CASH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">증권사·계좌종류</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">계좌/자산관리 › 계좌 관리 › 증권 마스터 수정에 등록된 이름만 사용할 수 있습니다</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">작성 예시</t>
+          <t xml:space="preserve">자산유형</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETF, STOCK, CRYPTO, GOLD, CASH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">키움 일반 | 키움증권 | QQQ | QQQ | NASDAQ | ETF | USD | 10 | 500 | 1300 | 나스닥1배</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">키움 일반 | 키움증권 | 현금 | CASH-KRW | CASH | CASH | KRW | 2000000 | 1 | (비움) | 현금성</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
+          <t xml:space="preserve">자산군</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASH(현금성), LEVERAGE(레버리지), NASDAQ100(나스닥1배), SP500(S&amp;P500), OTHER_STOCK(기타종목), GOLD(금), BLOCKCHAIN(블록체인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t xml:space="preserve">키움 일반 | 키움증권 | QQQ | QQQ | NASDAQ | ETF | USD | 10 | 500 | 1300 | 나스닥1배</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">키움 일반 | 키움증권 | 현금 | CASH-KRW | CASH | CASH | KRW | 2000000 | 1 | (비움) | 현금성</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t xml:space="preserve">주의</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t xml:space="preserve">이 파일은 업로드 시점의 '전체' 계좌·자산 현황으로 간주되어 현재 현황을 통째로 교체합니다. 이 '작성안내' 시트는 업로드 시 읽지 않습니다.</t>
         </is>

--- a/mock/sample_holdings_error.xlsx
+++ b/mock/sample_holdings_error.xlsx
@@ -56,55 +56,50 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">계좌종류</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">심볼</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t xml:space="preserve">종목명</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">심볼</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t xml:space="preserve">거래소</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">자산유형</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">통화</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">수량</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">평균매입가</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">매입평균환율</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자산군</t>
-        </is>
-      </c>
       <c r="L1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">계좌종류</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">비고</t>
         </is>
@@ -123,44 +118,44 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t xml:space="preserve">일반(위탁)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t xml:space="preserve">QQQ</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">QQQ</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">NASDAQ</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">ETF</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">USD</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">열주</t>
         </is>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>500</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>1300</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나스닥1배</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -176,39 +171,39 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t xml:space="preserve">일반(위탁)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t xml:space="preserve">VOO</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">VOO</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">NYSE</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">ETF</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">USD</t>
         </is>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>5</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>520</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S&amp;P500</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -224,39 +219,39 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t xml:space="preserve">일반(위탁)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">005930</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t xml:space="preserve">삼성전자</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">005930</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">KRX</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">STOCK</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">KRW</t>
         </is>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>100</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>70000</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타종목</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -272,39 +267,39 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t xml:space="preserve">일반(위탁)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">005930</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t xml:space="preserve">삼성전자</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">005930</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">KRX</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">STOCK</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">KRW</t>
         </is>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>50</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>71000</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기타종목</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -320,33 +315,38 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t xml:space="preserve">ISA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASH-KRW</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t xml:space="preserve">현금</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CASH-KRW</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t xml:space="preserve">CASH</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">CASH</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">KRW</t>
         </is>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>500000</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>1000</v>
       </c>
     </row>
@@ -363,39 +363,39 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t xml:space="preserve">ISA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">379800</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t xml:space="preserve">KODEX 미국S&amp;P500</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">379800</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">KRX</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">ETF</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">KRW</t>
         </is>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>300</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>18000</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">S&amp;P500</t>
-        </is>
       </c>
     </row>
     <row r="8">
@@ -411,39 +411,39 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t xml:space="preserve">가상자산</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BTC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t xml:space="preserve">비트코인</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BTC</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t xml:space="preserve">UPBIT</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">CRYPTO</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JPY</t>
-        </is>
-      </c>
-      <c r="H8">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="I8">
         <v>0.01</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>130000000</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">블록체인</t>
-        </is>
       </c>
     </row>
     <row r="9">
@@ -459,39 +459,189 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t xml:space="preserve">가상자산</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DOGE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t xml:space="preserve">도지코인</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DOGE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t xml:space="preserve">UPBIT</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve">CRYPTO</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve">KRW</t>
         </is>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>1000</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>300</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">밈코인</t>
-        </is>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미래 해외</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미래에셋증권</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해외주식</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">005930</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">삼성전자보통주</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KRX</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STOCK</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KRW</t>
+        </is>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+      <c r="J10">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미래 해외</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">미래에셋증권</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해외주식</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QQQ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QQQ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NYSE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETF</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>500</v>
+      </c>
+      <c r="K11">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가나다 계좌</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가나다증권</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일반(위탁)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VOO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NYSE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETF</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USD</t>
+        </is>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>500</v>
+      </c>
+      <c r="K12">
+        <v>1300</v>
       </c>
     </row>
   </sheetData>
@@ -509,7 +659,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">필수</t>
+          <t xml:space="preserve">입력</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -543,29 +693,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">필수</t>
+          <t xml:space="preserve">필수 · 선택</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">계좌의 증권사. 같은 계좌명은 같은 증권사여야 합니다</t>
+          <t xml:space="preserve">목록에서 고릅니다 (선택목록 시트 = 증권 마스터). 같은 계좌명은 같은 증권사여야 합니다</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">종목명</t>
+          <t xml:space="preserve">계좌종류</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">필수</t>
+          <t xml:space="preserve">선택</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">표시용 이름</t>
+          <t xml:space="preserve">목록에서 고릅니다 (예: 일반(위탁), ISA, 연금저축). 비우면 같은 이름 계좌의 기존 값 유지</t>
         </is>
       </c>
     </row>
@@ -582,82 +732,82 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">심볼 + 거래소로 종목 마스터와 매칭합니다 (예: QQQ/NASDAQ, 005930/KRX, CASH-KRW/CASH)</t>
+          <t xml:space="preserve">종목코드를 입력하면 종목명·거래소·자산유형·통화가 자동으로 채워집니다 (종목목록 시트 참고. 예: QQQ, 005930, CASH-KRW)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">거래소</t>
+          <t xml:space="preserve">종목명</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">필수</t>
+          <t xml:space="preserve">자동</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NASDAQ, NYSE, KRX, UPBIT, CASH 등</t>
+          <t xml:space="preserve">심볼로 자동 입력 (회색 칸). '(목록에 없음)'이 보이면 DB 에 없는 심볼입니다</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">자산유형</t>
+          <t xml:space="preserve">거래소</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 종목만</t>
+          <t xml:space="preserve">자동</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETF, STOCK, CRYPTO, GOLD, CASH</t>
+          <t xml:space="preserve">심볼로 자동 입력. 같은 심볼이 여러 거래소에 있으면 직접 바꿔 적습니다</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">통화</t>
+          <t xml:space="preserve">자산유형</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">필수</t>
+          <t xml:space="preserve">자동</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">KRW 또는 USD</t>
+          <t xml:space="preserve">심볼로 자동 입력</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">수량</t>
+          <t xml:space="preserve">통화</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">필수</t>
+          <t xml:space="preserve">자동</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0보다 큰 숫자. 현금은 금액을 수량에 적습니다</t>
+          <t xml:space="preserve">심볼로 자동 입력</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">평균매입가</t>
+          <t xml:space="preserve">수량</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -667,48 +817,48 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 이상, 원본통화 기준. 현금은 1</t>
+          <t xml:space="preserve">0보다 큰 숫자. 현금은 금액을 수량에 적습니다</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">매입평균환율</t>
+          <t xml:space="preserve">평균매입가</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">USD 필수</t>
+          <t xml:space="preserve">필수</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">USD 종목은 0보다 큰 값, KRW 종목은 비우거나 1</t>
+          <t xml:space="preserve">0 이상, 원본통화 기준. 현금은 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">자산군</t>
+          <t xml:space="preserve">매입평균환율</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">선택</t>
+          <t xml:space="preserve">USD 필수</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">신규 종목에만 적용 (코드 또는 한글명). 기존 종목은 무시하고 현재 매핑을 유지합니다</t>
+          <t xml:space="preserve">USD 종목은 0보다 큰 값, KRW 종목은 비우거나 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">계좌종류</t>
+          <t xml:space="preserve">비고</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -718,127 +868,45 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">증권 마스터에 등록된 계좌종류 (예: 일반(위탁), ISA, 연금저축). 비우면 같은 이름 계좌의 기존 값 유지</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">선택</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
           <t xml:space="preserve">계좌 메모. 계좌의 아무 행에 한 번만 적어도 됩니다. 비우면 기존 비고 유지</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">업로드 점검</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">심볼·종목명·거래소·자산유형·통화·증권사·계좌종류가 DB(종목 마스터·외부 종목 목록·증권 마스터)와 하나라도 다르면 반영하지 않고, 행 번호·입력값·DB 값을 보여 줍니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">허용값</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">통화</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KRW, USD</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">자산군</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자산군은 파일에서 바꾸지 않습니다. 계좌/자산관리 › 자산 구성 관리에서 정합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">거래소</t>
+          <t xml:space="preserve">주의</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">NASDAQ, NYSE, KRX, UPBIT, CASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">증권사·계좌종류</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">계좌/자산관리 › 계좌 관리 › 증권 마스터 수정에 등록된 이름만 사용할 수 있습니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자산유형</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ETF, STOCK, CRYPTO, GOLD, CASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자산군</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CASH(현금성), LEVERAGE(레버리지), NASDAQ100(나스닥1배), SP500(S&amp;P500), OTHER_STOCK(기타종목), GOLD(금), BLOCKCHAIN(블록체인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">키움 일반 | 키움증권 | QQQ | QQQ | NASDAQ | ETF | USD | 10 | 500 | 1300 | 나스닥1배</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">키움 일반 | 키움증권 | 현금 | CASH-KRW | CASH | CASH | KRW | 2000000 | 1 | (비움) | 현금성</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주의</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이 파일은 업로드 시점의 '전체' 계좌·자산 현황으로 간주되어 현재 현황을 통째로 교체합니다. 이 '작성안내' 시트는 업로드 시 읽지 않습니다.</t>
+          <t xml:space="preserve">이 파일은 업로드 시점의 '전체' 계좌·자산 현황으로 간주되어 현재 현황을 통째로 교체합니다. 이 '작성안내', '종목목록', '선택목록' 시트는 업로드 시 읽지 않습니다.</t>
         </is>
       </c>
     </row>

--- a/mock/sample_holdings_error.xlsx
+++ b/mock/sample_holdings_error.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 이상, 원본통화 기준. 현금은 1</t>
+          <t xml:space="preserve">0 이상, 원본통화 기준. 현금은 1 — 다른 값을 적어도 업로드할 때 경고 후 1로 바꿔 반영합니다</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">USD 종목은 0보다 큰 값, KRW 종목은 비우거나 1</t>
+          <t xml:space="preserve">USD 종목은 0보다 큰 값(필수). KRW 종목은 비우거나 1 — 다른 값을 적어도 업로드할 때 경고 후 1로 바꿔 반영합니다</t>
         </is>
       </c>
     </row>
